--- a/main/StructureDefinition-match-parameters-profile.xlsx
+++ b/main/StructureDefinition-match-parameters-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$78</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="272">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2026.1.0</t>
+    <t>2026.2.0-rc</t>
   </si>
   <si>
     <t>Name</t>
@@ -534,7 +534,7 @@
     <t>Parameters.parameter</t>
   </si>
   <si>
-    <t>5</t>
+    <t>8</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -731,6 +731,104 @@
   </si>
   <si>
     <t>Parameters.parameter:matchResult.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated</t>
+  </si>
+  <si>
+    <t>matchCreated</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreated.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType</t>
+  </si>
+  <si>
+    <t>matchCreationType</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://ths-greifswald.de/fhir/epix/ValueSet/MatchCreationTypeVS</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchCreationType.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority</t>
+  </si>
+  <si>
+    <t>matchPriority</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.value[x]</t>
+  </si>
+  <si>
+    <t>https://ths-greifswald.de/fhir/epix/ValueSet/MatchPriorityVS</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchPriority.part</t>
   </si>
   <si>
     <t>Parameters.parameter:linkId</t>
@@ -1082,12 +1180,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL54"/>
+  <dimension ref="A1:AL78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.93359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.50390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="16.40625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1110,7 +1208,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.48046875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.60546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -6936,8 +7034,2584 @@
         <v>21</v>
       </c>
     </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C55" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O57" s="2"/>
+      <c r="P57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y60" s="2"/>
+      <c r="Z60" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="D63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL54">
+  <autoFilter ref="A1:AL78">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6947,7 +9621,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI53">
+  <conditionalFormatting sqref="A2:AI77">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/StructureDefinition-match-parameters-profile.xlsx
+++ b/main/StructureDefinition-match-parameters-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="263">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-05</t>
+    <t>2026-09-16</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -534,7 +534,7 @@
     <t>Parameters.parameter</t>
   </si>
   <si>
-    <t>8</t>
+    <t>7</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -675,62 +675,35 @@
     <t>Parameters.parameter:matchItem.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:matchScore</t>
-  </si>
-  <si>
-    <t>matchScore</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.value[x]</t>
+    <t>Parameters.parameter:matchProbability</t>
+  </si>
+  <si>
+    <t>matchProbability</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
 </t>
   </si>
   <si>
-    <t>Parameters.parameter:matchScore.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchScore.part</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult</t>
-  </si>
-  <si>
-    <t>matchResult</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.value[x]</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:matchResult.part</t>
+    <t>Parameters.parameter:matchProbability.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchProbability.part</t>
   </si>
   <si>
     <t>Parameters.parameter:matchCreated</t>
@@ -1180,7 +1153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL78"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.546875" customWidth="true" bestFit="true"/>
@@ -5880,7 +5853,7 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>188</v>
@@ -5960,7 +5933,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>191</v>
@@ -6068,7 +6041,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>196</v>
@@ -6176,13 +6149,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>166</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>21</v>
@@ -6284,7 +6257,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>174</v>
@@ -6390,7 +6363,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>175</v>
@@ -6498,7 +6471,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>176</v>
@@ -6608,7 +6581,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>183</v>
@@ -6652,7 +6625,7 @@
         <v>21</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>21</v>
@@ -6714,7 +6687,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>186</v>
@@ -6740,7 +6713,7 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>188</v>
@@ -6773,13 +6746,11 @@
         <v>21</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>21</v>
+        <v>240</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>21</v>
@@ -6820,7 +6791,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>191</v>
@@ -6928,7 +6899,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>196</v>
@@ -7036,13 +7007,13 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>166</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>21</v>
@@ -7144,7 +7115,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>174</v>
@@ -7250,7 +7221,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>175</v>
@@ -7358,7 +7329,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>176</v>
@@ -7468,7 +7439,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>183</v>
@@ -7512,7 +7483,7 @@
         <v>21</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>21</v>
@@ -7574,7 +7545,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>186</v>
@@ -7600,7 +7571,7 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>188</v>
@@ -7633,11 +7604,11 @@
         <v>21</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>21</v>
@@ -7678,7 +7649,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>191</v>
@@ -7786,7 +7757,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>196</v>
@@ -7894,13 +7865,13 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>166</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D63" t="s" s="2">
         <v>21</v>
@@ -8002,7 +7973,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>174</v>
@@ -8108,7 +8079,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>175</v>
@@ -8216,7 +8187,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>176</v>
@@ -8326,7 +8297,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>183</v>
@@ -8370,7 +8341,7 @@
         <v>21</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>21</v>
@@ -8432,7 +8403,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>186</v>
@@ -8458,7 +8429,7 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="L68" t="s" s="2">
         <v>188</v>
@@ -8491,11 +8462,13 @@
         <v>21</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>259</v>
+        <v>21</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>21</v>
@@ -8536,7 +8509,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>191</v>
@@ -8644,7 +8617,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>196</v>
@@ -8750,868 +8723,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" hidden="true">
-      <c r="A71" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="B71" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="C71" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="D71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E71" s="2"/>
-      <c r="F71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G71" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K71" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q71" s="2"/>
-      <c r="R71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG71" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ71" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AK71" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL71" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" hidden="true">
-      <c r="A72" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="B72" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="C72" s="2"/>
-      <c r="D72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2"/>
-      <c r="F72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L72" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q72" s="2"/>
-      <c r="R72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF72" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AG72" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK72" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL72" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" hidden="true">
-      <c r="A73" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="C73" s="2"/>
-      <c r="D73" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="E73" s="2"/>
-      <c r="F73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L73" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O73" s="2"/>
-      <c r="P73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q73" s="2"/>
-      <c r="R73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF73" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="75" hidden="true">
-      <c r="A75" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="76" hidden="true">
-      <c r="A76" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="77" hidden="true">
-      <c r="A77" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="78" hidden="true">
-      <c r="A78" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AL78">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9621,7 +8734,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI77">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/StructureDefinition-match-parameters-profile.xlsx
+++ b/main/StructureDefinition-match-parameters-profile.xlsx
@@ -804,35 +804,35 @@
     <t>Parameters.parameter:matchPriority.part</t>
   </si>
   <si>
-    <t>Parameters.parameter:linkId</t>
-  </si>
-  <si>
-    <t>linkId</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.id</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.extension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.modifierExtension</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.name</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.value[x]</t>
+    <t>Parameters.parameter:matchLinkId</t>
+  </si>
+  <si>
+    <t>matchLinkId</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">integer
 </t>
   </si>
   <si>
-    <t>Parameters.parameter:linkId.resource</t>
-  </si>
-  <si>
-    <t>Parameters.parameter:linkId.part</t>
+    <t>Parameters.parameter:matchLinkId.resource</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:matchLinkId.part</t>
   </si>
 </sst>
 </file>
